--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521624</v>
+        <v>136046753</v>
       </c>
       <c r="B3" t="n">
-        <v>101326</v>
+        <v>104011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,53 +824,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>223284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slänst SV Halvarsbodarna, Dlr</t>
+          <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493867</v>
+        <v>493807</v>
       </c>
       <c r="R3" t="n">
-        <v>6670982</v>
+        <v>6670823</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,22 +878,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Naturvärdesträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,27 +907,861 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136046753</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136047747</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493900</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6671032</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136047747</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136048356</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>493919</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6671153</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136048356</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136048107</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493966</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6671051</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stöter tjäderhöna med 4? Kycklingar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136048107</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136046924</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493870</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6670906</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>12 blomstänglar Minst 100 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136046924</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136047204</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493897</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6670926</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136047204</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136049371</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493865</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6670919</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>22 blommande ex</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136049371</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121521624</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slänst SV Halvarsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493867</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6670982</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Christopher Magnusson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Christopher Magnusson, Justyna Ryniewicz</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>A240428 Fågelinventeringar Morgardshammar 1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121521624</t>
         </is>
@@ -948,6 +1771,13 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,64 +680,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521629</v>
+        <v>136055801</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slänt SV Halvarsbodarna, Dlr</t>
+          <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493711</v>
+        <v>493766</v>
       </c>
       <c r="R2" t="n">
-        <v>6670770</v>
+        <v>6670846</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,76 +764,87 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christopher Magnusson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christopher Magnusson, Justyna Ryniewicz</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>A240428 Fågelinventeringar Morgardshammar 1</t>
-        </is>
-      </c>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121521629</t>
+          <t>https://artportalen.se/Sighting/136055801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136046753</v>
+        <v>121521629</v>
       </c>
       <c r="B3" t="n">
-        <v>104011</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223284</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hökudden, Dlr</t>
+          <t>Slänt SV Halvarsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493807</v>
+        <v>493711</v>
       </c>
       <c r="R3" t="n">
-        <v>6670823</v>
+        <v>6670770</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +868,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Naturvärdesträd</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,33 +892,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Christopher Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Christopher Magnusson, Justyna Ryniewicz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>A240428 Fågelinventeringar Morgardshammar 1</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136046753</t>
+          <t>https://artportalen.se/Sighting/121521629</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136047747</v>
+        <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>104011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,44 +931,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>223284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493900</v>
+        <v>493807</v>
       </c>
       <c r="R4" t="n">
-        <v>6671032</v>
+        <v>6670823</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1010,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1000,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Naturvärdesträd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,16 +1031,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136047747</t>
+          <t>https://artportalen.se/Sighting/136046753</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136048356</v>
+        <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>104012</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,39 +1048,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>223284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493919</v>
+        <v>493725</v>
       </c>
       <c r="R5" t="n">
-        <v>6671153</v>
+        <v>6670771</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1125,19 +1105,14 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:17</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal sälgsolitär Naturvärdesträd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,16 +1138,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136048356</t>
+          <t>https://artportalen.se/Sighting/136055735</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136048107</v>
+        <v>136047747</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,26 +1155,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493966</v>
+        <v>493900</v>
       </c>
       <c r="R6" t="n">
-        <v>6671051</v>
+        <v>6671032</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1243,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stöter tjäderhöna med 4? Kycklingar</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,54 +1260,59 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136048107</t>
+          <t>https://artportalen.se/Sighting/136047747</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136046924</v>
+        <v>136048356</v>
       </c>
       <c r="B7" t="n">
-        <v>99292</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493870</v>
+        <v>493919</v>
       </c>
       <c r="R7" t="n">
-        <v>6670906</v>
+        <v>6671153</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>12 blomstänglar Minst 100 bladrosetter</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,51 +1377,56 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136046924</t>
+          <t>https://artportalen.se/Sighting/136048356</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136047204</v>
+        <v>136055892</v>
       </c>
       <c r="B8" t="n">
-        <v>99292</v>
+        <v>57979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493897</v>
+        <v>493847</v>
       </c>
       <c r="R8" t="n">
-        <v>6670926</v>
+        <v>6670914</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1475,19 +1456,9 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,51 +1484,55 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136047204</t>
+          <t>https://artportalen.se/Sighting/136055892</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136049371</v>
+        <v>136048107</v>
       </c>
       <c r="B9" t="n">
-        <v>99292</v>
+        <v>57169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493865</v>
+        <v>493966</v>
       </c>
       <c r="R9" t="n">
-        <v>6670919</v>
+        <v>6671051</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1589,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,12 +1574,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>22 blommande ex</t>
+          <t>Stöter tjäderhöna med 4? Kycklingar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,70 +1605,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136049371</t>
+          <t>https://artportalen.se/Sighting/136048107</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521624</v>
+        <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>101326</v>
+        <v>99292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slänst SV Halvarsbodarna, Dlr</t>
+          <t>Hökudden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493867</v>
+        <v>493870</v>
       </c>
       <c r="R10" t="n">
-        <v>6670982</v>
+        <v>6670906</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,22 +1676,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>12 blomstänglar Minst 100 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,27 +1705,486 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136046924</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136047204</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>493897</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6670926</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136047204</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136049371</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>493865</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6670919</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>22 blommande ex</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136049371</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136056088</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hökudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>493899</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6670950</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136056088</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121521624</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slänst SV Halvarsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>493867</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6670982</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Christopher Magnusson</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Christopher Magnusson, Justyna Ryniewicz</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>A240428 Fågelinventeringar Morgardshammar 1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121521624</t>
         </is>
@@ -1778,6 +2201,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104011</v>
+        <v>104012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99292</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99292</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99292</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104012</v>
+        <v>104014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104012</v>
+        <v>104014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136055801</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104015</v>
+        <v>104016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104015</v>
+        <v>104016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136047747</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136048356</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>136055892</v>
       </c>
       <c r="B8" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136048107</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136055801</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104016</v>
+        <v>104022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104016</v>
+        <v>104022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136047747</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136048356</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>136055892</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136048107</v>
       </c>
       <c r="B9" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136055801</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104022</v>
+        <v>104023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104022</v>
+        <v>104023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136047747</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136048356</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>136055892</v>
       </c>
       <c r="B8" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136048107</v>
       </c>
       <c r="B9" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104023</v>
+        <v>104034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104023</v>
+        <v>104034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136055801</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104034</v>
+        <v>104047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104034</v>
+        <v>104047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136047747</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136048356</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>136055892</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136048107</v>
       </c>
       <c r="B9" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104047</v>
+        <v>104048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104047</v>
+        <v>104048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136055801</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104048</v>
+        <v>104061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104048</v>
+        <v>104061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136047747</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136048356</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>136055892</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136048107</v>
       </c>
       <c r="B9" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104061</v>
+        <v>104062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104061</v>
+        <v>104062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
